--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\madhuresh.kumar\rmn_agent_work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aardra.menon\Documents\RMN\rmn_agent_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7C32F7-9DB8-48C9-B7DF-F53671F1DA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04604A81-6652-4B35-9963-1967C9D22AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,12 +52,10 @@
 In general, CPC is calculated by dividing the daily_spend (or total spend) by the number of clicks.</t>
   </si>
   <si>
-    <t>How is conversion_rate_percent defined in campaign_performance?</t>
-  </si>
-  <si>
-    <t>The conversion_rate_percent in the campaign_performance table is a FLOAT type. It is typically calculated as:
-( conversions / clicks ) * 100
-This represents the percentage of clicks that resulted in a conversion.</t>
+    <t>Show a bar chart of actual spend to date by channel.</t>
+  </si>
+  <si>
+    <t>Result: This bar chart effectively visualizes the actual spend to date across different channels. It clearly shows that 'Offsite' has the highest spend, followed by 'Onsite' and 'App', while 'Channel-CTV' and 'In-storeResult: This bar chart effectively visualizes the actual spend to date across different channels. It clearly shows that 'Offsite' has the highest spend, followed by 'Onsite' and 'App', while 'Channel-CTV' and 'In-store' represent significantly lower expenditures. This type of chart is useful for quickly identifying which channels are receiving the most investment.</t>
   </si>
 </sst>
 </file>
@@ -116,12 +114,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -431,7 +432,7 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="32.36328125" customWidth="1"/>
     <col min="2" max="2" width="43.1796875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -467,11 +468,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:2" ht="174" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
